--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.91097</v>
+        <v>17.19901</v>
       </c>
       <c r="D2" t="n">
-        <v>16.90805</v>
+        <v>16.72309</v>
       </c>
       <c r="E2" t="n">
-        <v>16.55175</v>
+        <v>16.94343</v>
       </c>
       <c r="F2" t="n">
-        <v>43.27251</v>
+        <v>42.37979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05114</v>
+        <v>0.05055</v>
       </c>
       <c r="H2" t="n">
-        <v>1.837</v>
+        <v>1.81973</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.88682</v>
+        <v>17.10842</v>
       </c>
       <c r="D3" t="n">
-        <v>16.68899</v>
+        <v>16.93791</v>
       </c>
       <c r="E3" t="n">
-        <v>17.05496</v>
+        <v>17.09755</v>
       </c>
       <c r="F3" t="n">
-        <v>43.69722</v>
+        <v>42.6154</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05076</v>
+        <v>0.05143</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88566</v>
+        <v>1.8322</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.98896</v>
+        <v>17.05553</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8459</v>
+        <v>16.6232</v>
       </c>
       <c r="E4" t="n">
-        <v>16.94248</v>
+        <v>16.63296</v>
       </c>
       <c r="F4" t="n">
-        <v>43.55452</v>
+        <v>43.95504</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05182</v>
+        <v>0.05173</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80802</v>
+        <v>1.85749</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.64285</v>
+        <v>16.71913</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06809</v>
+        <v>16.20654</v>
       </c>
       <c r="E6" t="n">
-        <v>16.4131</v>
+        <v>16.45577</v>
       </c>
       <c r="F6" t="n">
-        <v>21.81937</v>
+        <v>22.2503</v>
       </c>
       <c r="G6" t="n">
-        <v>34.6207</v>
+        <v>33.74604</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.75205</v>
+        <v>16.91213</v>
       </c>
       <c r="D7" t="n">
-        <v>16.16586</v>
+        <v>16.25801</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66619</v>
+        <v>16.44796</v>
       </c>
       <c r="F7" t="n">
-        <v>22.03983</v>
+        <v>21.5983</v>
       </c>
       <c r="G7" t="n">
-        <v>34.73915</v>
+        <v>34.81591</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.85761</v>
+        <v>16.84667</v>
       </c>
       <c r="D8" t="n">
-        <v>16.05703</v>
+        <v>16.01361</v>
       </c>
       <c r="E8" t="n">
-        <v>16.45177</v>
+        <v>16.37857</v>
       </c>
       <c r="F8" t="n">
-        <v>22.09311</v>
+        <v>22.01582</v>
       </c>
       <c r="G8" t="n">
-        <v>35.01309</v>
+        <v>34.25844</v>
       </c>
     </row>
   </sheetData>
